--- a/experiments/results/densenet101/CIFAR-100/baseline/msp/adaptive/avg/results.xlsx
+++ b/experiments/results/densenet101/CIFAR-100/baseline/msp/adaptive/avg/results.xlsx
@@ -353,7 +353,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O9"/>
+  <dimension ref="A1:O12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="61.33203125" customWidth="1" style="3" min="15" max="15"/>
@@ -813,6 +813,153 @@
       <c r="O9" s="5" t="inlineStr">
         <is>
           <t>dice_p=None,ash_p=None,react_th=None,scale_th=0.5,type=avg</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="n">
+        <v>67.48</v>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>85.75</v>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>82.61</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>73.02</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>76.67</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>77.12</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>74.56</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>79.95</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>21.41</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>96.7</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>74.67</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>77.47</v>
+      </c>
+      <c r="M10" s="5" t="n">
+        <v>66.23</v>
+      </c>
+      <c r="N10" s="5" t="n">
+        <v>81.67</v>
+      </c>
+      <c r="O10" s="5" t="inlineStr">
+        <is>
+          <t>dice_p=None,ash_p=None,react_th=None,scale_th=1.2,type=avg</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="n">
+        <v>65.41</v>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>86.70999999999999</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>82.55</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>72.56</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>76.69</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>72.04000000000001</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>82.84</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>24.76</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>95.98</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>74.84</v>
+      </c>
+      <c r="L11" s="5" t="n">
+        <v>76.78</v>
+      </c>
+      <c r="M11" s="5" t="n">
+        <v>66.05</v>
+      </c>
+      <c r="N11" s="5" t="n">
+        <v>81.95999999999999</v>
+      </c>
+      <c r="O11" s="5" t="inlineStr">
+        <is>
+          <t>dice_p=None,ash_p=None,react_th=None,scale_th=0.5,type=avg</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="n">
+        <v>67.09999999999999</v>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>85.98</v>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>82.63</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>72.87</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>76.61</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>77.17</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>73.87</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>80.77</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>22.08</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>96.58</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>74.63</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>77.39</v>
+      </c>
+      <c r="M12" s="5" t="n">
+        <v>66.15000000000001</v>
+      </c>
+      <c r="N12" s="5" t="n">
+        <v>81.79000000000001</v>
+      </c>
+      <c r="O12" s="5" t="inlineStr">
+        <is>
+          <t>dice_p=None,ash_p=None,react_th=None,scale_th=1.0,type=avg</t>
         </is>
       </c>
     </row>
